--- a/data/trans_orig/IP25B01_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Provincia-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>36344</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51833</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75460</t>
+          <t>75461</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27073</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46225</t>
+          <t>45312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25114</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41892</t>
+          <t>40551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>56217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80422</t>
+          <t>81949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>84576</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>34347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39774</t>
+          <t>39361</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133015</t>
+          <t>130570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28183</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>36088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>58720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54583</t>
+          <t>54567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34039</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58708</t>
+          <t>57920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105269</t>
+          <t>104346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33862</t>
+          <t>35175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>41827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>38254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70521</t>
+          <t>70619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>17188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>15414</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19742</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37017</t>
+          <t>36948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54740</t>
+          <t>54003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>29574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41465</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59284</t>
+          <t>58629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39378</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44654</t>
+          <t>51641</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34273</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48278</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91739</t>
+          <t>92126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>955</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21518</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14305</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>30018</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>42637</t>
+          <t>42960</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29126</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>50716</t>
+          <t>50474</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29018</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>43421</t>
+          <t>44115</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18663</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>48527</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>32608</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>64451</t>
+          <t>64260</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>29102</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>24965</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27971</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48949</t>
+          <t>48028</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45771</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51972</t>
+          <t>51551</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>58566</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>90675</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41217</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>60681</t>
+          <t>60761</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>52897</t>
+          <t>52143</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>77638</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>98738</t>
+          <t>102112</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>131188</t>
+          <t>134102</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>41171</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>69049</t>
+          <t>66731</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>87923</t>
+          <t>86094</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>86343</t>
+          <t>86475</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>107290</t>
+          <t>107527</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>160719</t>
+          <t>161146</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>190012</t>
+          <t>190352</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>27299</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>43202</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33689</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>52666</t>
+          <t>52128</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>65024</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>90768</t>
+          <t>91270</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>40257</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>152464</t>
+          <t>160064</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>115881</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>108760</t>
+          <t>111108</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>234273</t>
+          <t>238409</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>74195</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>112022</t>
+          <t>109903</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>88325</t>
+          <t>87914</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>123518</t>
+          <t>124397</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>171508</t>
+          <t>175662</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>224686</t>
+          <t>227935</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>212103</t>
+          <t>214427</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>271225</t>
+          <t>274063</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>267664</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>320955</t>
+          <t>321684</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>500908</t>
+          <t>500241</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>580998</t>
+          <t>578389</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>209396</t>
+          <t>208013</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>267429</t>
+          <t>266894</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>251124</t>
+          <t>251236</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>300815</t>
+          <t>303049</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>476781</t>
+          <t>474665</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>554660</t>
+          <t>559719</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B01_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos entre semana / solo 2023 en 2023 (tasa de respuesta: 98,33%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos entre semana en 2023 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4715</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4375</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30415</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24166</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36399</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>47,42%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>37,67%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>56,75%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27522</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18929</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>36344</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>49,92%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>23363</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43676</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>63398</t>
+          <t>53778</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51585</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75461</t>
+          <t>62528</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24536</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19044</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31377</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35559</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>26570</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45312</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>62,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40551</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67922</t>
+          <t>50025</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81949</t>
+          <t>58364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>72811</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72811</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72811</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56066</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>152177</t>
+          <t>120211</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152177</t>
+          <t>120211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152177</t>
+          <t>120211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42994</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84576</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>29629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>65452</t>
+          <t>40678</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39361</t>
+          <t>30956</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130570</t>
+          <t>54782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25298</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17648</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34463</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18163</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7843</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28761</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36088</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44992</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58720</t>
+          <t>52482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40834</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30733</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53463</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>39958</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21192</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54567</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>31,91%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45528</t>
+          <t>40158</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33771</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59574</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>85486</t>
+          <t>80992</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>67675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104346</t>
+          <t>95202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27849</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35737</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>31,02%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>24119</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12548</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>35175</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41827</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51639</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70619</t>
+          <t>63616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115191</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>115191</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>115191</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>125233</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125233</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125233</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>252063</t>
+          <t>214166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252063</t>
+          <t>214166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252063</t>
+          <t>214166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2917</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6794</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4566</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9286</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9694</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14890</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>25,08%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>10293</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6319</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15087</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>26,07%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17188</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>14184</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29640</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23135</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17727</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29313</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,37%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19464</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14444</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25384</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31924</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44989</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36948</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54003</t>
+          <t>50626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18177</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29041</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>23550</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18620</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29574</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>27904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>46096</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>57872</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>57872</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57872</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>125035</t>
+          <t>115581</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125035</t>
+          <t>115581</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125035</t>
+          <t>115581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51641</t>
+          <t>46192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9197</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3561</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17367</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7082</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12954</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13496</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7141</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>21711</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>11924</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>7135</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>17955</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>17003</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>34928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>34390</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>21096</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>44073</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>63,37%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>42239</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>35439</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>48785</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>65,22%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>54,72%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>75,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36943</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>35279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47172</t>
+          <t>49335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>79182</t>
+          <t>76988</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>60828</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92126</t>
+          <t>88947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,8%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>69550</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>69550</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>69550</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>64762</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>64762</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>64762</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>75614</t>
+          <t>65620</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>75614</t>
+          <t>65620</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75614</t>
+          <t>65620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>140376</t>
+          <t>135170</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>140376</t>
+          <t>135170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>140376</t>
+          <t>135170</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,107 +2996,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>12756</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>32,23%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>7853</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>13931</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12953</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>17371</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>32,73%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>43,89%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>17155</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12691</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>21283</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>49,71%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>36,77%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>61,67%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>24414</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>37447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>19123</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>14464</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>23723</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>48,32%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>36,54%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>59,94%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>16785</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>12562</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>21150</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>48,63%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>36,4%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>61,28%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>36111</t>
+          <t>36009</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>42960</t>
+          <t>42353</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,72 +3565,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2898</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>982</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>6494</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26695</t>
+          <t>25989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>20859</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>15552</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>26302</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>31,78%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>53,74%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>19038</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>13753</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>24110</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>41,24%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>40342</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>32777</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -3904,72 +3904,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>17907</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>13479</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>22925</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>36,59%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>14181</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>9890</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>19411</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>30,72%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>36124</t>
+          <t>30970</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>24191</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>44115</t>
+          <t>37620</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>27869</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>19653</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>41797</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>12093</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>7560</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>18585</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>15,59%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>32570</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>30987</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>64260</t>
+          <t>55455</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>15594</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>9385</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>24469</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>20506</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>14584</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>29102</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>24,41%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27687</t>
+          <t>27319</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48028</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>32326</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>24177</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>42375</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>17,48%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>30,64%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>35406</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>27237</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>46373</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>33034</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27686</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51551</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>73852</t>
+          <t>65359</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>58566</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>79169</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>62499</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>51411</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>72648</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>45,19%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>37,18%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>52,53%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>51218</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>42397</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>42,96%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>35,56%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>50,96%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>65012</t>
+          <t>49885</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>52143</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>77638</t>
+          <t>59639</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>116231</t>
+          <t>112383</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>102112</t>
+          <t>98205</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>134102</t>
+          <t>126188</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>138287</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>138287</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>138287</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>119223</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>119223</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>119223</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>152746</t>
+          <t>117443</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>152746</t>
+          <t>117443</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>152746</t>
+          <t>117443</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>271969</t>
+          <t>255730</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>271969</t>
+          <t>255730</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>271969</t>
+          <t>255730</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -4816,72 +4816,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>14956</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>22305</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>16793</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>10974</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>25356</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>30316</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>23802</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -4929,72 +4929,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>102121</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>91695</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>113134</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>64,18%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>57,63%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>71,1%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>77499</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>66731</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>86094</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>59,43%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>51,17%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>66,02%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>97808</t>
+          <t>83446</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>86475</t>
+          <t>71905</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>107527</t>
+          <t>92983</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>175307</t>
+          <t>185567</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>161146</t>
+          <t>170817</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>190352</t>
+          <t>200229</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -5042,72 +5042,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>39637</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>30825</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>48899</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>24,91%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>30,73%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>34846</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>27299</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>44211</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>26,72%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>33,9%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>42622</t>
+          <t>35093</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33706</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>52128</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>77468</t>
+          <t>74731</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>65024</t>
+          <t>63256</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>91270</t>
+          <t>87724</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -5155,57 +5155,57 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>130413</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>130413</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>130413</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>286850</t>
+          <t>298565</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>286850</t>
+          <t>298565</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>286850</t>
+          <t>298565</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5272,72 +5272,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>68791</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>51871</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>100354</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>68690</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>40413</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>160064</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>77863</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>34911</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>115881</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>146553</t>
+          <t>114766</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>111108</t>
+          <t>95411</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>238409</t>
+          <t>148465</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -5385,72 +5385,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>99687</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>83914</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>118822</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>91842</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>72606</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>109903</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>106017</t>
+          <t>91190</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>87914</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>107556</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>197859</t>
+          <t>190877</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>175662</t>
+          <t>167559</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>227935</t>
+          <t>215588</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -5498,72 +5498,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>276140</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>250839</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>300646</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>366</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>247965</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>214427</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>274063</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>38,09%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>42,1%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>293829</t>
+          <t>248695</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>268184</t>
+          <t>227158</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>321684</t>
+          <t>266924</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>541795</t>
+          <t>524834</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>500241</t>
+          <t>491685</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>578389</t>
+          <t>556119</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -5611,72 +5611,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>249572</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>225149</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>272680</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>242497</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>208013</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>266894</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>277350</t>
+          <t>229270</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>251236</t>
+          <t>211344</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>303049</t>
+          <t>251830</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>519847</t>
+          <t>478842</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>474665</t>
+          <t>446733</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>559719</t>
+          <t>508862</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -5724,57 +5724,57 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>919</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
